--- a/data/trans_bre/P1417-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1417-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>950,41%</t>
+          <t>575,27%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,12</t>
+          <t>-0,91; 2,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 4,03</t>
+          <t>0,29; 4,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,57</t>
+          <t>-0,24; 2,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,16</t>
+          <t>1,61; 4,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,39; —</t>
+          <t>-47,66; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>238,93; 4297,99</t>
+          <t>98,53; 2250,14</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,65</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>374,73%</t>
+          <t>309,12%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,72</t>
+          <t>0,12; 2,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,22</t>
+          <t>0,64; 4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,86</t>
+          <t>-0,92; 2,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,51</t>
+          <t>1,15; 4,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-93,24; —</t>
+          <t>-77,66; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,61; 1583,76</t>
+          <t>42,05; 1412,17</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>336,79%</t>
+          <t>206,28%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,66</t>
+          <t>0,61; 7,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,09</t>
+          <t>0,41; 3,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,35</t>
+          <t>0,81; 7,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,07</t>
+          <t>0,72; 6,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,3; 3177,97</t>
+          <t>-59,64; 3250,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,91; 1584,15</t>
+          <t>-1,46; 1584,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,5; 1622,63</t>
+          <t>22,49; 650,15</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>129,76%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,06</t>
+          <t>0,41; 2,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,83</t>
+          <t>0,67; 2,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,1</t>
+          <t>0,94; 3,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,2</t>
+          <t>0,67; 2,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,64; —</t>
+          <t>68,33; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,19; 811,21</t>
+          <t>53,3; 958,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,96; 1415,78</t>
+          <t>101,45; 1797,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 222,45</t>
+          <t>31,22; 313,4</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>142,9%</t>
+          <t>197,57%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,34</t>
+          <t>-0,96; 2,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,5</t>
+          <t>1,83; 5,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,48</t>
+          <t>2,23; 5,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,51</t>
+          <t>2,81; 6,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 420,46</t>
+          <t>-52,3; 470,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>104,82; 2250,01</t>
+          <t>80,33; 1991,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>173,17; 3392,82</t>
+          <t>168,26; 3475,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,21; 338,92</t>
+          <t>84,77; 435,68</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,79</t>
+          <t>1,2; 2,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,46</t>
+          <t>1,56; 3,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,34</t>
+          <t>-0,65; 2,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,22</t>
+          <t>3,37; 6,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,34; —</t>
+          <t>-55,52; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>3,21</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>274,67%</t>
+          <t>262,73%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,8</t>
+          <t>0,84; 1,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,92</t>
+          <t>1,7; 2,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,45</t>
+          <t>1,31; 2,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,86</t>
+          <t>2,61; 3,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>120,22; 661,52</t>
+          <t>125,93; 703,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>268,24; 1008,21</t>
+          <t>244,53; 1001,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>153,97; 596,67</t>
+          <t>157,9; 622,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>163,25; 434,09</t>
+          <t>175,77; 389,22</t>
         </is>
       </c>
     </row>
